--- a/artfynd/A 29661-2025 artfynd.xlsx
+++ b/artfynd/A 29661-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ138"/>
+  <dimension ref="A1:AZ151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19878,10 +19878,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>14685537</v>
+        <v>137282069</v>
       </c>
       <c r="B134" t="n">
-        <v>61589</v>
+        <v>43474</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -19889,37 +19889,52 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>101526</v>
+        <v>100942</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tandsnäcka</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Perforatella bidentata</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Gmelin, 1788)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Juglansbo, 1,3 km SO om vägskälet, Gstr</t>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615195</v>
+        <v>615054</v>
       </c>
       <c r="R134" t="n">
-        <v>6686224</v>
+        <v>6686322</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -19943,12 +19958,27 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2006-06-16</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2006-06-16</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -19959,74 +19989,88 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>Källpåverkad stråk</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Jens Hansen</t>
+          <t>Göran Vesslén</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Ted Von Proschwitz</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr"/>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14685537</t>
+          <t>https://artportalen.se/Sighting/137282069</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>14685536</v>
+        <v>137282072</v>
       </c>
       <c r="B135" t="n">
-        <v>61742</v>
+        <v>43474</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>101967</v>
+        <v>100942</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kalkkärrsgrynsnäcka</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Vertigo geyeri</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Lindholm, 1925</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Juglansbo, 1,3 km SO om vägskälet, Gstr</t>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615195</v>
+        <v>615054</v>
       </c>
       <c r="R135" t="n">
-        <v>6686224</v>
+        <v>6686338</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -20050,12 +20094,27 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2006-06-16</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2006-06-16</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -20066,88 +20125,88 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>Källpåverkad stråk</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Jens Hansen</t>
+          <t>Göran Vesslén</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Ted Von Proschwitz</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr"/>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14685536</t>
+          <t>https://artportalen.se/Sighting/137282072</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>65530043</v>
+        <v>137282083</v>
       </c>
       <c r="B136" t="n">
-        <v>99142</v>
+        <v>43474</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219847</v>
+        <v>100942</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Gundbo gruvor 10 km SSO om Hedesunda, Gstr</t>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615083</v>
+        <v>615068</v>
       </c>
       <c r="R136" t="n">
-        <v>6686145</v>
+        <v>6686251</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -20171,17 +20230,27 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2006-06-25</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2006-06-25</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ca. 10 blommande plantor, på/vid en äldre patrullväg, utan bärlager.</t>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -20192,84 +20261,88 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>Äldre patrullväg (utan bärlager), i äldre, örtrik kraftledningsgata.</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Göran Vesslén</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr"/>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/65530043</t>
+          <t>https://artportalen.se/Sighting/137282083</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>65530644</v>
+        <v>137282084</v>
       </c>
       <c r="B137" t="n">
-        <v>99029</v>
+        <v>43474</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>223578</v>
+        <v>100942</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr"/>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gundbo 8,5 km SSO om Hedesunda, Gstr</t>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>615056</v>
+        <v>615068</v>
       </c>
       <c r="R137" t="n">
-        <v>6686344</v>
+        <v>6686255</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -20293,17 +20366,27 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2006-06-19</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2006-06-19</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>7 blommande plantor, på/vid en äldre patrullväg, utan bärlager.</t>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -20314,84 +20397,88 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>Äldre patrullväg (utan bärlager), i äldre, örtrik kraftledningsgata.</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Göran Vesslén</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr"/>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/65530644</t>
+          <t>https://artportalen.se/Sighting/137282084</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>65530646</v>
+        <v>137282086</v>
       </c>
       <c r="B138" t="n">
-        <v>99029</v>
+        <v>43474</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>223578</v>
+        <v>100942</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr"/>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gundbo 8,5 km SSO om Hedesunda, Gstr</t>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>615056</v>
+        <v>615055</v>
       </c>
       <c r="R138" t="n">
-        <v>6686369</v>
+        <v>6686319</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -20415,17 +20502,27 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2006-06-19</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2006-06-19</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>3 blommande plantor, på/vid en äldre patrullväg, utan bärlager.</t>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -20436,25 +20533,1696 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>Äldre patrullväg (utan bärlager), i äldre, örtrik kraftledningsgata.</t>
-        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282086</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137282088</v>
+      </c>
+      <c r="B139" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>615055</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6686323</v>
+      </c>
+      <c r="S139" t="n">
+        <v>5</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282088</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>137282094</v>
+      </c>
+      <c r="B140" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>615053</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6686332</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282094</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>137282096</v>
+      </c>
+      <c r="B141" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>615057</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6686346</v>
+      </c>
+      <c r="S141" t="n">
+        <v>5</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282096</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>137282097</v>
+      </c>
+      <c r="B142" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>615055</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6686354</v>
+      </c>
+      <c r="S142" t="n">
+        <v>5</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282097</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>137282098</v>
+      </c>
+      <c r="B143" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>615054</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6686354</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282098</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>137282099</v>
+      </c>
+      <c r="B144" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>615052</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6686357</v>
+      </c>
+      <c r="S144" t="n">
+        <v>5</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282099</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>137282100</v>
+      </c>
+      <c r="B145" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>615052</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6686374</v>
+      </c>
+      <c r="S145" t="n">
+        <v>5</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282100</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>137282101</v>
+      </c>
+      <c r="B146" t="n">
+        <v>43474</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Jugansbo Gunbo gruvor, Gstr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>615049</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6686378</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>17 grader varmt, klart, 2-3 m/s, nordlig vind, 100% sol.</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282101</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>14685537</v>
+      </c>
+      <c r="B147" t="n">
+        <v>61589</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>101526</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Tandsnäcka</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Perforatella bidentata</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Gmelin, 1788)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Juglansbo, 1,3 km SO om vägskälet, Gstr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>615195</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6686224</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2006-06-16</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2006-06-16</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>Källpåverkad stråk</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Jens Hansen</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Ted Von Proschwitz</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14685537</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>14685536</v>
+      </c>
+      <c r="B148" t="n">
+        <v>61742</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>101967</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Kalkkärrsgrynsnäcka</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Vertigo geyeri</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Lindholm, 1925</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Juglansbo, 1,3 km SO om vägskälet, Gstr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>615195</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6686224</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2006-06-16</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2006-06-16</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>Källpåverkad stråk</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Jens Hansen</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Ted Von Proschwitz</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14685536</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>65530043</v>
+      </c>
+      <c r="B149" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Gundbo gruvor 10 km SSO om Hedesunda, Gstr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>615083</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6686145</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2006-06-25</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2006-06-25</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Ca. 10 blommande plantor, på/vid en äldre patrullväg, utan bärlager.</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>Äldre patrullväg (utan bärlager), i äldre, örtrik kraftledningsgata.</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
           <t>Gillis Aronsson</t>
         </is>
       </c>
-      <c r="AX138" t="inlineStr">
+      <c r="AX149" t="inlineStr">
         <is>
           <t>Gillis Aronsson</t>
         </is>
       </c>
-      <c r="AY138" t="inlineStr"/>
-      <c r="AZ138" t="inlineStr">
+      <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65530043</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>65530644</v>
+      </c>
+      <c r="B150" t="n">
+        <v>99029</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>223578</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Äkta ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Gundbo 8,5 km SSO om Hedesunda, Gstr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>615056</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6686344</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2006-06-19</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2006-06-19</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>7 blommande plantor, på/vid en äldre patrullväg, utan bärlager.</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>Äldre patrullväg (utan bärlager), i äldre, örtrik kraftledningsgata.</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65530644</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>65530646</v>
+      </c>
+      <c r="B151" t="n">
+        <v>99029</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>223578</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Äkta ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Gundbo 8,5 km SSO om Hedesunda, Gstr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>615056</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6686369</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2006-06-19</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2006-06-19</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>3 blommande plantor, på/vid en äldre patrullväg, utan bärlager.</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>Äldre patrullväg (utan bärlager), i äldre, örtrik kraftledningsgata.</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/65530646</t>
         </is>
@@ -20599,6 +22367,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29661-2025 artfynd.xlsx
+++ b/artfynd/A 29661-2025 artfynd.xlsx
@@ -19881,7 +19881,7 @@
         <v>137282069</v>
       </c>
       <c r="B134" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>137282072</v>
       </c>
       <c r="B135" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>137282083</v>
       </c>
       <c r="B136" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>137282084</v>
       </c>
       <c r="B137" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>137282086</v>
       </c>
       <c r="B138" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>137282088</v>
       </c>
       <c r="B139" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>137282094</v>
       </c>
       <c r="B140" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>137282096</v>
       </c>
       <c r="B141" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>137282097</v>
       </c>
       <c r="B142" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>137282098</v>
       </c>
       <c r="B143" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>137282099</v>
       </c>
       <c r="B144" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>137282100</v>
       </c>
       <c r="B145" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>137282101</v>
       </c>
       <c r="B146" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 29661-2025 artfynd.xlsx
+++ b/artfynd/A 29661-2025 artfynd.xlsx
@@ -19881,7 +19881,7 @@
         <v>137282069</v>
       </c>
       <c r="B134" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>137282072</v>
       </c>
       <c r="B135" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>137282083</v>
       </c>
       <c r="B136" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>137282084</v>
       </c>
       <c r="B137" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>137282086</v>
       </c>
       <c r="B138" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>137282088</v>
       </c>
       <c r="B139" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>137282094</v>
       </c>
       <c r="B140" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>137282096</v>
       </c>
       <c r="B141" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>137282097</v>
       </c>
       <c r="B142" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>137282098</v>
       </c>
       <c r="B143" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>137282099</v>
       </c>
       <c r="B144" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>137282100</v>
       </c>
       <c r="B145" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>137282101</v>
       </c>
       <c r="B146" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
